--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104484_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104484_W3.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9562</v>
+        <v>3.5804</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7007</v>
+        <v>4.1191</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7446</v>
+        <v>-0.5387</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1258</v>
+        <v>1.1323</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6002</v>
+        <v>1.5998</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4744</v>
+        <v>-0.4674</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2739</v>
+        <v>2.2636</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1992</v>
+        <v>2.1891</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.148</v>
+        <v>-1.1312</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6696</v>
+        <v>0.2903</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1735</v>
+        <v>0.6083</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5039</v>
+        <v>-0.3181</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.928</v>
+        <v>1.4788</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3974</v>
+        <v>-0.2159</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5306</v>
+        <v>1.6948</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.4605</v>
+        <v>-3.449</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7013</v>
+        <v>-1.6976</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7592</v>
+        <v>-1.7514</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.8998</v>
+        <v>-1.9182</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.3374</v>
+        <v>-1.352</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5625</v>
+        <v>-0.5662</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5606</v>
+        <v>-1.5309</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5402</v>
+        <v>0.0765</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3388</v>
+        <v>-0.2491</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2014</v>
+        <v>0.3256</v>
       </c>
       <c r="V3" t="n">
-        <v>3.0337</v>
+        <v>3.0303</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8484</v>
+        <v>0.8512999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>B. BURJANADZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1755</v>
+        <v>0.3624</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1238</v>
+        <v>-0.1278</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0517</v>
+        <v>0.4902</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.8128</v>
+        <v>-1.4314</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4268</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.386</v>
+        <v>-1.5087</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1304</v>
+        <v>-0.9043</v>
       </c>
       <c r="K4" t="n">
-        <v>0.432</v>
+        <v>-0.1519</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5625</v>
+        <v>-0.7524</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6824</v>
+        <v>-0.5271</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8588</v>
+        <v>0.2292</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8236</v>
+        <v>-0.7563</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8691</v>
+        <v>0.4495</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1765</v>
+        <v>0.1925</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6926</v>
+        <v>0.257</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3461</v>
+        <v>2.0271</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3461</v>
+        <v>1.9497</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. BURJANADZE</t>
+          <t>J. KLJAJIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>0.3404</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.764</v>
+        <v>1.1939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8139999999999999</v>
+        <v>-0.8535</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4404</v>
+        <v>-0.1087</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0735</v>
+        <v>0.7156</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.514</v>
+        <v>-0.8243</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8947000000000001</v>
+        <v>1.4658</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1456</v>
+        <v>1.1614</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.749</v>
+        <v>0.3045</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5458</v>
+        <v>-1.5745</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2192</v>
+        <v>-0.4458</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7649</v>
+        <v>-1.1287</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1334</v>
+        <v>-0.4901</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4688</v>
+        <v>0.0044</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6021</v>
+        <v>-0.4945</v>
       </c>
       <c r="V5" t="n">
-        <v>2.0376</v>
+        <v>1.1669</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9604</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KLJAJIC</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3091</v>
+        <v>0.0275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6294</v>
+        <v>1.5282</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9385</v>
+        <v>-1.5007</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.09</v>
+        <v>2.0138</v>
       </c>
       <c r="H6" t="n">
-        <v>0.723</v>
+        <v>-1.9333</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8131</v>
+        <v>3.9471</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5057</v>
+        <v>3.6329</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1806</v>
+        <v>-0.5968</v>
       </c>
       <c r="L6" t="n">
-        <v>0.325</v>
+        <v>4.2297</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5957</v>
+        <v>-1.6191</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4576</v>
+        <v>-1.3365</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1381</v>
+        <v>-0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.162</v>
+        <v>-0.6783</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6079</v>
+        <v>-0.6902</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5541</v>
+        <v>0.0119</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1698</v>
+        <v>-0.6251</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0771</v>
+        <v>-1.7146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. TOMAS</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3732</v>
+        <v>-0.2655</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.0411</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3732</v>
+        <v>-0.2244</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2159</v>
+        <v>-2.8228</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-1.4437</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2159</v>
+        <v>-1.3791</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.3955</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5662</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2159</v>
+        <v>-2.6521</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.8392</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2159</v>
+        <v>-0.8129</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1573</v>
+        <v>0.4482</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1573</v>
+        <v>0.379</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>P. TOMAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5829</v>
+        <v>-0.3724</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1476</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7305</v>
+        <v>-0.3724</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0147</v>
+        <v>-0.2144</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9409</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9556</v>
+        <v>-0.2144</v>
       </c>
       <c r="J8" t="n">
-        <v>3.663</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2487</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6484</v>
+        <v>-0.2144</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3552</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2931</v>
+        <v>-0.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2872</v>
+        <v>-0.1579</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.113</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1742</v>
+        <v>-0.1579</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6299</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.173</v>
+        <v>-1.3955</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8346</v>
+        <v>-0.9732</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3385</v>
+        <v>-0.4223</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7526</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6754</v>
+        <v>-0.6722</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9226</v>
+        <v>0.9064</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6752</v>
+        <v>-1.6467</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1434</v>
+        <v>-0.0999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3962</v>
+        <v>-0.5138</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5395</v>
+        <v>0.4138</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7906</v>
+        <v>-0.7829</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7906</v>
+        <v>-0.7829</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4282</v>
+        <v>-1.7253</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9003</v>
+        <v>-1.2461</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5279</v>
+        <v>-0.4792</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6064</v>
+        <v>-2.5975</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7778</v>
+        <v>-0.7729</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8285</v>
+        <v>-1.8246</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4315</v>
+        <v>-1.4386</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1749</v>
+        <v>-1.1588</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5024</v>
+        <v>0.1892</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4688</v>
+        <v>0.1925</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1413</v>
+        <v>-2.2223</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8198</v>
+        <v>-1.131</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3214</v>
+        <v>-1.0913</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3955</v>
+        <v>-2.3941</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1243</v>
+        <v>-0.1099</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2711</v>
+        <v>-2.2842</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5262</v>
+        <v>-0.5593</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7663</v>
+        <v>1.7582</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.2926</v>
+        <v>-2.3175</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8692</v>
+        <v>-1.8348</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8906</v>
+        <v>-1.8681</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1995</v>
+        <v>-0.2834</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2521</v>
+        <v>-0.523</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0526</v>
+        <v>0.2396</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8980000000000001</v>
+        <v>-0.1915000000000009</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6802</v>
+        <v>3.106100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5783</v>
+        <v>-3.2975</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.6336</v>
+        <v>-10.6122</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.2498</v>
+        <v>-4.236899999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.383799999999999</v>
+        <v>-6.3751</v>
       </c>
       <c r="J12" t="n">
-        <v>3.482599999999999</v>
+        <v>3.2776</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0032</v>
+        <v>2.8789</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4789999999999996</v>
+        <v>0.3986999999999998</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.1161</v>
+        <v>-13.8896</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.252899999999999</v>
+        <v>-7.1159</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.863</v>
+        <v>-6.7738</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2684</v>
+        <v>2.2764</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.2075</v>
+        <v>-10.2434</v>
       </c>
       <c r="R12" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9526999999999999</v>
+        <v>-0.2559</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.617999999999999</v>
+        <v>-0.9092000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6650999999999999</v>
+        <v>0.6531</v>
       </c>
       <c r="V12" t="n">
-        <v>8.4201</v>
+        <v>8.4002</v>
       </c>
       <c r="W12" t="n">
-        <v>11.0233</v>
+        <v>10.981</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.6033</v>
+        <v>-2.5809</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4095</v>
+        <v>4.6696</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6985</v>
+        <v>4.9601</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2889</v>
+        <v>-0.2905</v>
       </c>
       <c r="G13" t="n">
-        <v>4.7367</v>
+        <v>4.7324</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1054</v>
+        <v>3.0966</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6313</v>
+        <v>1.6358</v>
       </c>
       <c r="J13" t="n">
-        <v>5.4606</v>
+        <v>5.4331</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5948</v>
+        <v>3.5713</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7239</v>
+        <v>-0.7007</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2192</v>
+        <v>0.4819</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8257</v>
+        <v>0.1204</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3935</v>
+        <v>0.3616</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2663</v>
+        <v>2.9712</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3346</v>
+        <v>2.8847</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9317</v>
+        <v>0.0866</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2855</v>
+        <v>3.2139</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4933</v>
+        <v>2.2496</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2079</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7621</v>
+        <v>3.5538</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9914</v>
+        <v>2.2506</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2293</v>
+        <v>1.3033</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5233</v>
+        <v>-0.34</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5019</v>
+        <v>-0.0009</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0214</v>
+        <v>-0.3391</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3802</v>
+        <v>-0.015</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.747</v>
+        <v>-0.3929</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3668</v>
+        <v>0.3779</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0593</v>
+        <v>2.4581</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5725</v>
+        <v>1.4308</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5132</v>
+        <v>1.0272</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2186</v>
+        <v>2.293</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2642</v>
+        <v>2.4984</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9543</v>
+        <v>-0.2055</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5879</v>
+        <v>1.7435</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2818</v>
+        <v>1.9822</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>-0.2388</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3693</v>
+        <v>0.5495</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0176</v>
+        <v>0.5162</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3517</v>
+        <v>0.0333</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9324</v>
+        <v>-0.2007</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.747</v>
+        <v>-0.6298</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1854</v>
+        <v>0.4291</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9367</v>
+        <v>1.5539</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1082</v>
+        <v>-1.0031</v>
       </c>
       <c r="F16" t="n">
-        <v>1.045</v>
+        <v>2.5571</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6627</v>
+        <v>0.6736</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2223</v>
+        <v>-1.6659</v>
       </c>
       <c r="I16" t="n">
-        <v>0.885</v>
+        <v>2.3396</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6353</v>
+        <v>-0.1047</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.111</v>
+        <v>-2.1966</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7463</v>
+        <v>2.0918</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0274</v>
+        <v>0.7784</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1113</v>
+        <v>0.5306</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>0.2477</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7277</v>
+        <v>-0.0498</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4567</v>
+        <v>-0.3929</v>
       </c>
       <c r="U16" t="n">
-        <v>0.271</v>
+        <v>0.343</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.8603</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8399</v>
+        <v>0.5612</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3099</v>
+        <v>-0.4764</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1499</v>
+        <v>1.0376</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6855</v>
+        <v>0.6726</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6681</v>
+        <v>-0.2185</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3535</v>
+        <v>0.8911</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0697</v>
+        <v>0.6273</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1859</v>
+        <v>-0.1174</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1162</v>
+        <v>0.7447</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7551</v>
+        <v>0.0452</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5178</v>
+        <v>-0.1011</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2373</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7794</v>
+        <v>0.3439</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.747</v>
+        <v>0.1043</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0324</v>
+        <v>0.2396</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8678</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3983</v>
+        <v>0.1941</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0136</v>
+        <v>-1.2691</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4119</v>
+        <v>1.4632</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8381</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0273</v>
+        <v>0.0368</v>
       </c>
       <c r="I18" t="n">
-        <v>0.805</v>
+        <v>0.8012</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4317</v>
+        <v>0.4205</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1385</v>
+        <v>0.1379</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4006</v>
+        <v>0.4176</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>1.084</v>
+        <v>0.8827</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5263</v>
+        <v>0.2925</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5577</v>
+        <v>0.5903</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8877</v>
+        <v>-1.5269</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0616</v>
+        <v>1.7786</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1739</v>
+        <v>-3.3054</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.6311</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8585</v>
+        <v>0.6145</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1201</v>
+        <v>0.0166</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8096</v>
+        <v>1.8926</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9697</v>
+        <v>1.7064</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1601</v>
+        <v>0.1862</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0712</v>
+        <v>-1.2615</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1113</v>
+        <v>-1.092</v>
       </c>
       <c r="O19" t="n">
-        <v>0.04</v>
+        <v>-0.1695</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.131</v>
+        <v>-0.6423</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3378</v>
+        <v>-0.5283</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0597</v>
+        <v>-1.7709</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4322</v>
+        <v>-2.7429</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4919</v>
+        <v>0.9719</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.7295</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6118</v>
+        <v>0.8642</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0107</v>
+        <v>-0.1347</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9009</v>
+        <v>0.7856</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7144</v>
+        <v>0.9653</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1866</v>
+        <v>-0.1796</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2785</v>
+        <v>-0.0562</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1026</v>
+        <v>-0.1011</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1759</v>
+        <v>0.0449</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1508</v>
+        <v>0.0035</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.1176</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.8924</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.8924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6522</v>
+        <v>-3.4086</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.158</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4942</v>
+        <v>-2.6208</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5844</v>
+        <v>-1.6024</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9953</v>
+        <v>-1.0156</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0582</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0182</v>
+        <v>-0.0527</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.04</v>
+        <v>-0.0449</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5261</v>
+        <v>-1.5048</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5712</v>
+        <v>0.828</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0344</v>
+        <v>0.448</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.3801</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4125</v>
+        <v>-4.0235</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8081</v>
+        <v>-1.4773</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6044</v>
+        <v>-2.5462</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5641</v>
+        <v>-1.5695</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2251</v>
+        <v>-2.2231</v>
       </c>
       <c r="I22" t="n">
-        <v>0.661</v>
+        <v>0.6536</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3442</v>
+        <v>-0.3645</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.1225</v>
+        <v>-1.1311</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2198</v>
+        <v>-1.205</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2755</v>
+        <v>0.1103</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3297</v>
+        <v>0.0253</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8979000000000017</v>
+        <v>1.678200000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>3.578399999999999</v>
+        <v>3.2976</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6802</v>
+        <v>-1.6193</v>
       </c>
       <c r="G23" t="n">
-        <v>10.6336</v>
+        <v>10.6123</v>
       </c>
       <c r="H23" t="n">
-        <v>4.249700000000001</v>
+        <v>4.237</v>
       </c>
       <c r="I23" t="n">
-        <v>6.383699999999999</v>
+        <v>6.375099999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>14.116</v>
+        <v>13.8896</v>
       </c>
       <c r="K23" t="n">
-        <v>7.252999999999998</v>
+        <v>7.1159</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8629</v>
+        <v>6.7737</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.4824</v>
+        <v>-3.2775</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.0035</v>
+        <v>-2.879</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4791</v>
+        <v>-0.3986000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2684</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-12.4759</v>
+        <v>-12.5199</v>
       </c>
       <c r="R23" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9527999999999999</v>
+        <v>1.7425</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6652000000000001</v>
+        <v>-0.6532999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6179</v>
+        <v>2.3958</v>
       </c>
       <c r="V23" t="n">
-        <v>-8.419799999999999</v>
+        <v>-8.4001</v>
       </c>
       <c r="W23" t="n">
-        <v>2.6033</v>
+        <v>2.5808</v>
       </c>
       <c r="X23" t="n">
-        <v>-11.0233</v>
+        <v>-10.9811</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104484_W3.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104484_W3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.8512999999999999</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.7146</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.7829</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-2.5809</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104484_W3.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-10.9811</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
